--- a/frontend/docs/reviews/dossiers-phase-three/list.xlsx
+++ b/frontend/docs/reviews/dossiers-phase-three/list.xlsx
@@ -24,19 +24,19 @@
     <t>قائمة الإضبارات · مشفى محمد بن زايد الإماراتي</t>
   </si>
   <si>
-    <t>رقم التقرير: DOS-19-2026-000002</t>
-  </si>
-  <si>
-    <t>الإصدار: 2026-09-15 13:49:34 · Asia/Damascus</t>
+    <t>رقم التقرير: DOS-37-2026-000002</t>
+  </si>
+  <si>
+    <t>الإصدار: 2026-09-15 15:07:46 · Asia/Damascus</t>
   </si>
   <si>
     <t>المنشأة: منشأة اختبار الخدمات</t>
   </si>
   <si>
-    <t>أصدره: Diego Sawayn DVM</t>
-  </si>
-  <si>
-    <t>نطاق التقرير: البحث: PH3-ellussbd | الحالة: الكل | ورمي: الكل | الزيارات: الكل | من: الكل | إلى: الكل | الترتيب: الكل | الاتجاه: الكل</t>
+    <t>أصدره: Paris Lakin</t>
+  </si>
+  <si>
+    <t>نطاق التقرير: البحث: PH3-ict6ccul | الحالة: الكل | ورمي: الكل | الزيارات: الكل | من: الكل | إلى: الكل | الترتيب: الكل | الاتجاه: الكل</t>
   </si>
   <si>
     <t>نطاق التقرير: جميع النتائج المطابقة للفلاتر؛ لا تقتصر على الصفحة المعروضة.</t>
@@ -75,10 +75,10 @@
     <t>تاريخ آخر زيارة</t>
   </si>
   <si>
-    <t>PH3-ellussbd-1440</t>
-  </si>
-  <si>
-    <t>P-91960710-79ee-4c03-8afb-572f98af67b4</t>
+    <t>PH3-ict6ccul-1440</t>
+  </si>
+  <si>
+    <t>P-aebc68d7-ef77-46cc-9fe7-3af10bf3c878</t>
   </si>
   <si>
     <t>ليلى اختبار اصطناعي</t>
@@ -96,16 +96,16 @@
     <t>فعالة</t>
   </si>
   <si>
-    <t>PH3-ellussbd-768</t>
-  </si>
-  <si>
-    <t>P-a71f270f-8a84-4e23-b46e-9ed63a46b54f</t>
-  </si>
-  <si>
-    <t>PH3-ellussbd-390</t>
-  </si>
-  <si>
-    <t>P-b1243cc7-cb60-46fe-96fb-654722bdbaa7</t>
+    <t>PH3-ict6ccul-768</t>
+  </si>
+  <si>
+    <t>P-b06ea0a3-9f85-4463-b0f5-bbdfdddf21b5</t>
+  </si>
+  <si>
+    <t>PH3-ict6ccul-390</t>
+  </si>
+  <si>
+    <t>P-a8b88db1-7a64-43b7-9de6-58084020413a</t>
   </si>
   <si>
     <t>مسودة — غير مكتملة</t>
@@ -828,10 +828,11 @@
     <mergeCell ref="A6:K6"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.47" right="0.47" top="0.35" bottom="0.5" header="0.3" footer="0.2"/>
+  <pageMargins left="0.47" right="0.47" top="0.5" bottom="0.5" header="0.18" footer="0.2"/>
   <pageSetup paperSize="9" orientation="landscape" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
   <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddFooter>&amp;"Cairo,Regular"&amp;9&amp;CDOS-19-2026-000002 | &amp;P / &amp;N</oddFooter>
+    <oddHeader>&amp;R&amp;"Cairo,Regular"&amp;9قائمة الإضبارات</oddHeader>
+    <oddFooter>&amp;C&amp;"Cairo,Regular"&amp;9DOS-37-2026-000002 | &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
